--- a/reports/Debug-purgatory-20260111/For Winter Ending (Actual)_Budget.xlsx
+++ b/reports/Debug-purgatory-20260111/For Winter Ending (Actual)_Budget.xlsx
@@ -34,15 +34,117 @@
     <t>D6215</t>
   </si>
   <si>
+    <t>D1010</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>D1500</t>
+  </si>
+  <si>
+    <t>D4053</t>
+  </si>
+  <si>
+    <t>D4055</t>
+  </si>
+  <si>
+    <t>D5205</t>
+  </si>
+  <si>
+    <t>D5207</t>
+  </si>
+  <si>
+    <t>D6710</t>
+  </si>
+  <si>
+    <t>D6750</t>
+  </si>
+  <si>
+    <t>D8060</t>
+  </si>
+  <si>
+    <t>99150</t>
+  </si>
+  <si>
+    <t>D1100</t>
+  </si>
+  <si>
+    <t>D5000</t>
+  </si>
+  <si>
+    <t>D5201</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8030</t>
+  </si>
+  <si>
+    <t>D8040</t>
+  </si>
+  <si>
     <t>99200</t>
   </si>
   <si>
     <t>D8050</t>
   </si>
   <si>
+    <t>99100</t>
+  </si>
+  <si>
+    <t>D2000</t>
+  </si>
+  <si>
+    <t>D2200</t>
+  </si>
+  <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>D5202</t>
+  </si>
+  <si>
+    <t>D5209</t>
+  </si>
+  <si>
+    <t>D7010</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
     <t>D6780</t>
   </si>
   <si>
+    <t>D1000</t>
+  </si>
+  <si>
+    <t>D4054</t>
+  </si>
+  <si>
+    <t>D5206</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6720</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>D6800</t>
+  </si>
+  <si>
     <t>D1030</t>
   </si>
   <si>
@@ -55,108 +157,6 @@
     <t>D5810</t>
   </si>
   <si>
-    <t>D1000</t>
-  </si>
-  <si>
-    <t>D4054</t>
-  </si>
-  <si>
-    <t>D5206</t>
-  </si>
-  <si>
-    <t>D6700</t>
-  </si>
-  <si>
-    <t>D6720</t>
-  </si>
-  <si>
-    <t>D6730</t>
-  </si>
-  <si>
-    <t>D6790</t>
-  </si>
-  <si>
-    <t>D6800</t>
-  </si>
-  <si>
-    <t>99100</t>
-  </si>
-  <si>
-    <t>D2000</t>
-  </si>
-  <si>
-    <t>D2200</t>
-  </si>
-  <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>D5202</t>
-  </si>
-  <si>
-    <t>D5209</t>
-  </si>
-  <si>
-    <t>D7010</t>
-  </si>
-  <si>
-    <t>D8020</t>
-  </si>
-  <si>
-    <t>99150</t>
-  </si>
-  <si>
-    <t>D1100</t>
-  </si>
-  <si>
-    <t>D5000</t>
-  </si>
-  <si>
-    <t>D5201</t>
-  </si>
-  <si>
-    <t>D8010</t>
-  </si>
-  <si>
-    <t>D8030</t>
-  </si>
-  <si>
-    <t>D8040</t>
-  </si>
-  <si>
-    <t>D1010</t>
-  </si>
-  <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>D1500</t>
-  </si>
-  <si>
-    <t>D4053</t>
-  </si>
-  <si>
-    <t>D4055</t>
-  </si>
-  <si>
-    <t>D5205</t>
-  </si>
-  <si>
-    <t>D5207</t>
-  </si>
-  <si>
-    <t>D6710</t>
-  </si>
-  <si>
-    <t>D6750</t>
-  </si>
-  <si>
-    <t>D8060</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -190,15 +190,117 @@
     <t>Housekeeping</t>
   </si>
   <si>
+    <t>Lift Operations</t>
+  </si>
+  <si>
+    <t>Terrain Park</t>
+  </si>
+  <si>
+    <t>Ski Patrol</t>
+  </si>
+  <si>
+    <t>Tickets</t>
+  </si>
+  <si>
+    <t>Expert Edge</t>
+  </si>
+  <si>
+    <t>Purg Sports Main Ave</t>
+  </si>
+  <si>
+    <t>Waffle Cabin</t>
+  </si>
+  <si>
+    <t>Paradise</t>
+  </si>
+  <si>
+    <t>Accounting/Mgmt Services</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>IT Services</t>
+  </si>
+  <si>
+    <t>Comp Tickets</t>
+  </si>
+  <si>
+    <t>Vehicle Maintenance</t>
+  </si>
+  <si>
+    <t>F&amp;B Admin</t>
+  </si>
+  <si>
+    <t>Powderhouse</t>
+  </si>
+  <si>
+    <t>General Administration</t>
+  </si>
+  <si>
+    <t>Executive</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
     <t>Winter Season Pass Visits  - Home Resort</t>
   </si>
   <si>
     <t>Risk Management</t>
   </si>
   <si>
+    <t>Daily Winter Ticketed</t>
+  </si>
+  <si>
+    <t>Ski School</t>
+  </si>
+  <si>
+    <t>Child Care</t>
+  </si>
+  <si>
+    <t>Rentals</t>
+  </si>
+  <si>
+    <t>Dante's</t>
+  </si>
+  <si>
+    <t>Village Market Deli</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
     <t>Grounds Maintenance</t>
   </si>
   <si>
+    <t>Mountain G&amp;A</t>
+  </si>
+  <si>
+    <t>Purg Sports Resort</t>
+  </si>
+  <si>
+    <t>Hoody's</t>
+  </si>
+  <si>
+    <t>Resort Services G&amp;A</t>
+  </si>
+  <si>
+    <t>Guest Services</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Commercial Tenants</t>
+  </si>
+  <si>
     <t>Snowmaking</t>
   </si>
   <si>
@@ -209,108 +311,6 @@
   </si>
   <si>
     <t>Events</t>
-  </si>
-  <si>
-    <t>Mountain G&amp;A</t>
-  </si>
-  <si>
-    <t>Purg Sports Resort</t>
-  </si>
-  <si>
-    <t>Hoody's</t>
-  </si>
-  <si>
-    <t>Resort Services G&amp;A</t>
-  </si>
-  <si>
-    <t>Guest Services</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Commercial Tenants</t>
-  </si>
-  <si>
-    <t>Daily Winter Ticketed</t>
-  </si>
-  <si>
-    <t>Ski School</t>
-  </si>
-  <si>
-    <t>Child Care</t>
-  </si>
-  <si>
-    <t>Rentals</t>
-  </si>
-  <si>
-    <t>Dante's</t>
-  </si>
-  <si>
-    <t>Village Market Deli</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>Accounting</t>
-  </si>
-  <si>
-    <t>Comp Tickets</t>
-  </si>
-  <si>
-    <t>Vehicle Maintenance</t>
-  </si>
-  <si>
-    <t>F&amp;B Admin</t>
-  </si>
-  <si>
-    <t>Powderhouse</t>
-  </si>
-  <si>
-    <t>General Administration</t>
-  </si>
-  <si>
-    <t>Executive</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>Lift Operations</t>
-  </si>
-  <si>
-    <t>Terrain Park</t>
-  </si>
-  <si>
-    <t>Ski Patrol</t>
-  </si>
-  <si>
-    <t>Tickets</t>
-  </si>
-  <si>
-    <t>Expert Edge</t>
-  </si>
-  <si>
-    <t>Purg Sports Main Ave</t>
-  </si>
-  <si>
-    <t>Waffle Cabin</t>
-  </si>
-  <si>
-    <t>Paradise</t>
-  </si>
-  <si>
-    <t>Accounting/Mgmt Services</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>IT Services</t>
   </si>
 </sst>
 </file>
@@ -746,7 +746,7 @@
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>2296585.21</v>
+        <v>630890.07</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>56</v>
@@ -799,10 +799,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2">
-        <v>59980.00</v>
+        <v>223870.24</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>58</v>
@@ -816,7 +816,7 @@
         <v>48</v>
       </c>
       <c r="C10" s="2">
-        <v>16359.12</v>
+        <v>45555.70</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>59</v>
@@ -827,10 +827,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="2">
-        <v>42943.12</v>
+        <v>240169.39</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>60</v>
@@ -838,16 +838,16 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="2">
-        <v>99366.90</v>
+        <v>55575.33</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -855,10 +855,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2">
-        <v>120106.20</v>
+        <v>6791034.99</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>61</v>
@@ -869,10 +869,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2">
-        <v>212890.42</v>
+        <v>29607.02</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>62</v>
@@ -883,10 +883,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" s="2">
-        <v>8707.50</v>
+        <v>124740.41</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>62</v>
@@ -897,10 +897,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" s="2">
-        <v>141910.72</v>
+        <v>149255.70</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>63</v>
@@ -911,10 +911,10 @@
         <v>11</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2">
-        <v>719487.72</v>
+        <v>32822.88</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>63</v>
@@ -928,7 +928,7 @@
         <v>48</v>
       </c>
       <c r="C18" s="2">
-        <v>14490.00</v>
+        <v>10615.76</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>64</v>
@@ -942,7 +942,7 @@
         <v>49</v>
       </c>
       <c r="C19" s="2">
-        <v>43000.00</v>
+        <v>41128.30</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>64</v>
@@ -956,7 +956,7 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>25455.28</v>
+        <v>58800.36</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>65</v>
@@ -964,16 +964,16 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2">
-        <v>28175.50</v>
+        <v>174040.59</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -981,10 +981,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2">
-        <v>593054.03</v>
+        <v>85725.36</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>66</v>
@@ -992,16 +992,16 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C23" s="2">
-        <v>30172.72</v>
+        <v>125672.40</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1009,10 +1009,10 @@
         <v>15</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" s="2">
-        <v>62993.75</v>
+        <v>74264.48</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>67</v>
@@ -1020,16 +1020,16 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C25" s="2">
-        <v>31666.96</v>
+        <v>117776.88</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1037,10 +1037,10 @@
         <v>16</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" s="2">
-        <v>51848.64</v>
+        <v>57728.32</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>68</v>
@@ -1051,10 +1051,10 @@
         <v>17</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C27" s="2">
-        <v>28178.64</v>
+        <v>12183.00</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>69</v>
@@ -1062,394 +1062,394 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C28" s="2">
-        <v>54076.90</v>
+        <v>95139.36</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C29" s="2">
-        <v>13603.70</v>
+        <v>76759.92</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C30" s="2">
-        <v>15930.00</v>
+        <v>43466.32</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C31" s="2">
-        <v>60162.25</v>
+        <v>225564.15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="2">
-        <v>47856.16</v>
+        <v>23120.64</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33" s="2">
-        <v>7927.00</v>
+        <v>88989.52</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C34" s="2">
-        <v>46638.00</v>
+        <v>58107.12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C35" s="2">
-        <v>267111.95</v>
+        <v>59980.00</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="2">
-        <v>1195308.92</v>
+        <v>16359.12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C37" s="2">
-        <v>16800.36</v>
+        <v>46638.00</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" s="2">
-        <v>32076.27</v>
+        <v>267111.95</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C39" s="2">
-        <v>1186937.10</v>
+        <v>1195308.92</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C40" s="2">
-        <v>85617.52</v>
+        <v>16800.36</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="2">
-        <v>274475.48</v>
+        <v>32076.27</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C42" s="2">
-        <v>72749.43</v>
+        <v>1186937.10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43" s="2">
-        <v>116201.79</v>
+        <v>85617.52</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C44" s="2">
-        <v>20645.65</v>
+        <v>257760.80</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C45" s="2">
-        <v>52460.16</v>
+        <v>72749.43</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C46" s="2">
-        <v>51037.08</v>
+        <v>98747.29</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C47" s="2">
-        <v>12183.00</v>
+        <v>20645.65</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C48" s="2">
-        <v>95139.36</v>
+        <v>52460.16</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C49" s="2">
-        <v>76759.92</v>
+        <v>51037.08</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C50" s="2">
-        <v>43466.32</v>
+        <v>42943.12</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C51" s="2">
-        <v>235560.77</v>
+        <v>99366.90</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C52" s="2">
-        <v>23120.64</v>
+        <v>25455.28</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C53" s="2">
-        <v>88989.52</v>
+        <v>28175.50</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C54" s="2">
-        <v>58107.12</v>
+        <v>467600.93</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C55" s="2">
-        <v>223870.24</v>
+        <v>30172.72</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1457,10 +1457,10 @@
         <v>37</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C56" s="2">
-        <v>45555.70</v>
+        <v>62993.75</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>89</v>
@@ -1474,7 +1474,7 @@
         <v>48</v>
       </c>
       <c r="C57" s="2">
-        <v>240169.39</v>
+        <v>31666.96</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>90</v>
@@ -1482,16 +1482,16 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C58" s="2">
-        <v>55575.33</v>
+        <v>51848.64</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1499,10 +1499,10 @@
         <v>39</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C59" s="2">
-        <v>6987049.79</v>
+        <v>28178.64</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>91</v>
@@ -1510,16 +1510,16 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C60" s="2">
-        <v>29607.02</v>
+        <v>54076.90</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1527,10 +1527,10 @@
         <v>40</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C61" s="2">
-        <v>124740.41</v>
+        <v>13603.70</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>92</v>
@@ -1538,16 +1538,16 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C62" s="2">
-        <v>188438.72</v>
+        <v>15930.00</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1558,7 +1558,7 @@
         <v>48</v>
       </c>
       <c r="C63" s="2">
-        <v>32822.88</v>
+        <v>60162.25</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>93</v>
@@ -1566,16 +1566,16 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C64" s="2">
-        <v>10615.76</v>
+        <v>47856.16</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1586,7 +1586,7 @@
         <v>49</v>
       </c>
       <c r="C65" s="2">
-        <v>44370.34</v>
+        <v>7927.00</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>94</v>
@@ -1600,7 +1600,7 @@
         <v>48</v>
       </c>
       <c r="C66" s="2">
-        <v>58800.36</v>
+        <v>120106.20</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>95</v>
@@ -1608,16 +1608,16 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C67" s="2">
-        <v>194410.75</v>
+        <v>167271.60</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1628,7 +1628,7 @@
         <v>48</v>
       </c>
       <c r="C68" s="2">
-        <v>85725.36</v>
+        <v>8707.50</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>96</v>
@@ -1636,16 +1636,16 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C69" s="2">
-        <v>125672.40</v>
+        <v>141910.72</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1653,10 +1653,10 @@
         <v>45</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C70" s="2">
-        <v>74264.48</v>
+        <v>689767.94</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>97</v>
@@ -1664,16 +1664,16 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C71" s="2">
-        <v>117776.88</v>
+        <v>14490.00</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1681,10 +1681,10 @@
         <v>46</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C72" s="2">
-        <v>57728.32</v>
+        <v>43000.00</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>98</v>
